--- a/关键词库.xlsx
+++ b/关键词库.xlsx
@@ -5,18 +5,21 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Onesummer_D\Learning\Competitons\TiaoZhanBei\项目\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Onesummer_D\Learning\Competitons\TiaoZhanBei\项目\法学产出物\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABC2187F-ADF8-4A6C-B2E8-01722A6BF9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E99524C1-FFDE-4ED3-B126-5B6BA89DF9E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5290" yWindow="7160" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4750" yWindow="5900" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$5</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -64,22 +67,10 @@
     <t>公益诉讼</t>
   </si>
   <si>
-    <t xml:space="preserve">河水发黑发臭、刺鼻气味、粉尘噪音扰民、土壤重金属、污水直排、偷排废液、非法倾倒固废、垃圾填埋污染地下水、工厂冒黑烟、雾霾来源、扬尘污染、占用河道、占用农用地、挖沙采石、破坏林地、破坏耕地、食物中毒、集体腹泻、过期食品翻新、生产日期造假、药品副作用群体事件、虚假宣传保健品坑害老人、外卖不卫生、无证经营、黑作坊、病死猪肉、地沟油、非法添加、转基因食品未标注、疫苗问题、猎杀野生动物、非法采矿致土地破坏、生态修复费、诉中修复、非法倾倒建筑生活垃圾、惩罚性赔偿金、化工厂排污致饮用水源污染、多次反映、一直没人管、大家都投诉、环境污染严重
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">检察院、公益诉讼、起诉、检察建议、环境督察
 </t>
   </si>
   <si>
-    <t xml:space="preserve">支持起诉、弱势群体、打不起官司、没钱打官司、讨薪无门、维权困难、老年人赡养、残疾人权益、未成年人保护、撤销监护权、家庭暴力、校园欺凌、工伤赔偿纠纷、追索扶养费、追索赡养费、家庭暴力受害人请求离婚、军人军属权益受侵害、撤销监护权、申请法律援助被拒、法律咨询、协调法律援助、恶意欠薪、拒不支付劳动报酬、农民工工资、劳务费
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">农民工、建筑工人、清洁工、保安、老年人（60岁以上）、残疾人、未成年人、留守儿童、妇女、被家暴、低保户、五保户、退伍军人优抚、找不到老板、拿不到工资、干完活不给钱、帮忙写诉状、不会打官司、收集不了证据、法院要证据我没有、公司注销了告谁、老板跑了、申请法律援助被拒、不知道被告身份信息、确认劳动关系、追索抚养费、追索赡养费、大风刮倒围挡砸车、免费停车场车辆受损、防盗门砸伤业主、十级伤残、农村建房施工合同纠纷、墙壁发霉跳闸、承揽人质量不合格、讨薪、工程款、拖欠工资、多次讨要未果、没签合同
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">检察院支持起诉、出具意见书、协助调查取证、跟进审理进度
 </t>
   </si>
@@ -87,25 +78,41 @@
     <t>行政执法监督</t>
   </si>
   <si>
-    <t xml:space="preserve">打了12345没人管、投诉了没下文、反映了一年没动静、职能部门说不归他管、违法建筑还在建没人拆、噪音超标环保说测不了、无证经营举报了还在开、占道经营没人赶、违法停车交警不管、虚假处罚决定书、滥用职权强拆、村务公开监督、镇政府不履行村务公开督办职责、棚户区改造强拆、帮拆名义强拆、暴力拖出控制、破坏监控、合法宅基地被拆、工伤认定不予受理、猴疱疹病毒感染、病毒性脑炎死亡、行政复议维持、罚款太重、处罚不公平、同样情况罚得不一样、小本生意罚不起
-</t>
-  </si>
-  <si>
     <t>市场监督管理局、生态环境局、自然资源局、城管局、住建局、卫健委、教育局、人社局、公安局派出所（不作为）、消防大队
 、督促履职、纠正违法、整改落实、行政公益诉讼、发出检察建议</t>
   </si>
   <si>
-    <t xml:space="preserve">污染环境、生态破坏、损害社会公共利益、侵害众多消费者权益、食品药品安全、英雄烈士名誉、文物保护、非法排污、非法占地、非法采矿、滥伐林木、非法捕捞、侵害众多消费者合法权益、省级以上消费者协会、侵害英烈名誉荣誉、生态修复费用、惩罚性赔偿、国有财产保护、国有土地使用权出让、重复投诉、持续污染、群体性事件、国有资产流失、非法排污、食品药品安全
+    <t>民事支持起诉</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">河水发黑发臭、刺鼻气味、粉尘噪音扰民、土壤重金属、污水直排、偷排废液、非法倾倒固废、垃圾填埋污染地下水、工厂冒黑烟、雾霾来源、扬尘污染、占用河道、占用农用地、挖沙采石、破坏林地、破坏耕地、食物中毒、集体腹泻、过期食品翻新、生产日期造假、药品副作用群体事件、虚假宣传保健品坑害老人、外卖不卫生、无证经营、黑作坊、病死猪肉、地沟油、非法添加、转基因食品未标注、疫苗问题、猎杀野生动物、非法采矿致土地破坏、生态修复费、诉中修复、非法倾倒建筑生活垃圾、惩罚性赔偿金、化工厂排污致饮用水源污染、环境污染严重
 </t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">行政不作为、乱作为、懒政怠政、选择性执法、违法审批、违规许可、查处不力、取缔不力、相互推诿、踢皮球、不履行法定职责、检察建议、行政机关违法行使职权、行政争议实质性化解、抗诉、再审检察建议、纠正违法检察建议、社会治理检察建议、行刑双向衔接、行政违法行为监督、公开听证、释法说理、司法救助、小过重罚、过罚不当、同案不同罚、行政处罚畸重、首违不罚
+    <t xml:space="preserve">污染环境、生态破坏、损害社会公共利益、侵害众多消费者权益、食品药品安全、英雄烈士名誉、文物保护、非法排污、非法占地、非法采矿、滥伐林木、非法捕捞、侵害众多消费者合法权益、省级以上消费者协会、侵害英烈名誉荣誉、生态修复费用、惩罚性赔偿、国有财产保护、国有土地使用权出让、重复投诉、持续污染、群体性事件、国有资产流失、非法排污、食品药品安全、多次反映、一直没人管、大家都投诉
 </t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>民事支持起诉</t>
+    <t xml:space="preserve">建筑工人、清洁工、保安、老年人（60岁以上）、残疾人、未成年人、留守儿童、妇女、被家暴、低保户、五保户、退伍军人优抚、帮忙写诉状、不会打官司、收集不了证据、法院要证据我没有、公司注销了告谁、老板跑了、申请法律援助被拒、不知道被告身份信息、确认劳动关系、追索抚养费、追索赡养费、大风刮倒围挡砸车、免费停车场车辆受损、防盗门砸伤业主、十级伤残、农村建房施工合同纠纷、墙壁发霉跳闸、承揽人质量不合格、工程款、多次讨要未果、没签合同
+</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>支持起诉、弱势群体、打不起官司、没钱打官司、讨薪无门、维权困难、老年人赡养、残疾人权益、未成年人保护、撤销监护权、家庭暴力、校园欺凌、工伤赔偿纠纷、追索扶养费、追索赡养费、家庭暴力受害人请求离婚、军人军属权益受侵害、撤销监护权、申请法律援助被拒、法律咨询、协调法律援助、恶意欠薪、拒不支付劳动报酬、农民工工资、劳务费
+、农民工、拖欠工资、讨薪、干完活不给钱、拿不到工资、找不到老板</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">职能部门说不归他管、违法建筑还在建没人拆、噪音超标环保说测不了、无证经营举报了还在开、占道经营没人赶、违法停车交警不管、虚假处罚决定书、滥用职权强拆、村务公开监督、镇政府不履行村务公开督办职责、棚户区改造强拆、帮拆名义强拆、暴力拖出控制、破坏监控、合法宅基地被拆、工伤认定不予受理、猴疱疹病毒感染、病毒性脑炎死亡、行政复议维持、处罚不公平
+</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>行政不作为、乱作为、懒政怠政、选择性执法、违法审批、违规许可、查处不力、取缔不力、相互推诿、踢皮球、不履行法定职责、检察建议、行政机关违法行使职权、行政争议实质性化解、抗诉、再审检察建议、纠正违法检察建议、社会治理检察建议、行刑双向衔接、行政违法行为监督、公开听证、释法说理、司法救助、小过重罚、过罚不当、同案不同罚、行政处罚畸重、首违不罚
+、罚款太重、小本生意罚不起、同样情况罚得不一样、首违免罚、初次轻微违法、罚款与违法情节不相当、违法所得很少但罚款很高、反映了一年没动静</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -515,44 +522,45 @@
         <v>8</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>9</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="2" customFormat="1" ht="272" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:4" s="2" customFormat="1" ht="250" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="D5" s="5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D5" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/关键词库.xlsx
+++ b/关键词库.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Onesummer_D\Learning\Competitons\TiaoZhanBei\项目\法学产出物\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E99524C1-FFDE-4ED3-B126-5B6BA89DF9E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AFE80B4-EA63-40D5-A0DD-CE6FA3968E68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4750" yWindow="5900" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5020" yWindow="5880" windowWidth="19200" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>线索分类类型</t>
   </si>
@@ -55,64 +55,70 @@
     <t>刑事犯罪</t>
   </si>
   <si>
-    <t>诈骗、盗窃、抢劫、抢夺、故意伤害、杀人、强奸、猥亵、非法拘禁、绑架、敲诈勒索、寻衅滋事、聚众斗殴、涉黑、涉恶、村霸、保护伞、黄赌毒、制毒、贩毒、容留吸毒、开设赌场、组织卖淫、强迫卖淫、拒不支付劳动报酬（恶意欠薪）、危险驾驶、醉酒驾车、危害公共安全、放火、决水、爆炸、投放危险物质、侵犯公民个人信息、非法集资、组织领导传销活动、高空抛物、扔垃圾砸车、走私精神药品、三唑仑、咪达唑仑、失火罪、上坟祭扫引发山火、烧毁侧柏、一级森林防火区、毒品</t>
-  </si>
-  <si>
-    <t>被打、被抢、被偷、被骗钱、被威胁、被跟踪、被骚扰、非法拘禁、限制自由、强行带走、动手打人、聚众闹事、拉横幅恐吓、发现尸体、发现血迹、伪造公章、造假证、恶意拨打12345、辱骂接线员、多次无故占用公共资源、以举报为要挟索要财物、封口费、虚假投诉骗取赔偿、非法剥夺人身自由、转移财产逃匿、经责令支付仍不支付</t>
+    <t>公益诉讼</t>
+  </si>
+  <si>
+    <t>行政执法监督</t>
+  </si>
+  <si>
+    <t>民事支持起诉</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>排除词/降噪词</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>公安</t>
-  </si>
-  <si>
-    <t>公益诉讼</t>
-  </si>
-  <si>
-    <t xml:space="preserve">检察院、公益诉讼、起诉、检察建议、环境督察
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">检察院支持起诉、出具意见书、协助调查取证、跟进审理进度
-</t>
-  </si>
-  <si>
-    <t>行政执法监督</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>检察院、公益诉讼、起诉、检察建议、环境督察</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>检察院支持起诉、出具意见书、协助调查取证、跟进审理进度</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>市场监督管理局、生态环境局、自然资源局、城管局、住建局、卫健委、教育局、人社局、公安局派出所（不作为）、消防大队
 、督促履职、纠正违法、整改落实、行政公益诉讼、发出检察建议</t>
-  </si>
-  <si>
-    <t>民事支持起诉</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">河水发黑发臭、刺鼻气味、粉尘噪音扰民、土壤重金属、污水直排、偷排废液、非法倾倒固废、垃圾填埋污染地下水、工厂冒黑烟、雾霾来源、扬尘污染、占用河道、占用农用地、挖沙采石、破坏林地、破坏耕地、食物中毒、集体腹泻、过期食品翻新、生产日期造假、药品副作用群体事件、虚假宣传保健品坑害老人、外卖不卫生、无证经营、黑作坊、病死猪肉、地沟油、非法添加、转基因食品未标注、疫苗问题、猎杀野生动物、非法采矿致土地破坏、生态修复费、诉中修复、非法倾倒建筑生活垃圾、惩罚性赔偿金、化工厂排污致饮用水源污染、环境污染严重
-</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">污染环境、生态破坏、损害社会公共利益、侵害众多消费者权益、食品药品安全、英雄烈士名誉、文物保护、非法排污、非法占地、非法采矿、滥伐林木、非法捕捞、侵害众多消费者合法权益、省级以上消费者协会、侵害英烈名誉荣誉、生态修复费用、惩罚性赔偿、国有财产保护、国有土地使用权出让、重复投诉、持续污染、群体性事件、国有资产流失、非法排污、食品药品安全、多次反映、一直没人管、大家都投诉
-</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">建筑工人、清洁工、保安、老年人（60岁以上）、残疾人、未成年人、留守儿童、妇女、被家暴、低保户、五保户、退伍军人优抚、帮忙写诉状、不会打官司、收集不了证据、法院要证据我没有、公司注销了告谁、老板跑了、申请法律援助被拒、不知道被告身份信息、确认劳动关系、追索抚养费、追索赡养费、大风刮倒围挡砸车、免费停车场车辆受损、防盗门砸伤业主、十级伤残、农村建房施工合同纠纷、墙壁发霉跳闸、承揽人质量不合格、工程款、多次讨要未果、没签合同
-</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>支持起诉、弱势群体、打不起官司、没钱打官司、讨薪无门、维权困难、老年人赡养、残疾人权益、未成年人保护、撤销监护权、家庭暴力、校园欺凌、工伤赔偿纠纷、追索扶养费、追索赡养费、家庭暴力受害人请求离婚、军人军属权益受侵害、撤销监护权、申请法律援助被拒、法律咨询、协调法律援助、恶意欠薪、拒不支付劳动报酬、农民工工资、劳务费
-、农民工、拖欠工资、讨薪、干完活不给钱、拿不到工资、找不到老板</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">职能部门说不归他管、违法建筑还在建没人拆、噪音超标环保说测不了、无证经营举报了还在开、占道经营没人赶、违法停车交警不管、虚假处罚决定书、滥用职权强拆、村务公开监督、镇政府不履行村务公开督办职责、棚户区改造强拆、帮拆名义强拆、暴力拖出控制、破坏监控、合法宅基地被拆、工伤认定不予受理、猴疱疹病毒感染、病毒性脑炎死亡、行政复议维持、处罚不公平
-</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>行政不作为、乱作为、懒政怠政、选择性执法、违法审批、违规许可、查处不力、取缔不力、相互推诿、踢皮球、不履行法定职责、检察建议、行政机关违法行使职权、行政争议实质性化解、抗诉、再审检察建议、纠正违法检察建议、社会治理检察建议、行刑双向衔接、行政违法行为监督、公开听证、释法说理、司法救助、小过重罚、过罚不当、同案不同罚、行政处罚畸重、首违不罚
-、罚款太重、小本生意罚不起、同样情况罚得不一样、首违免罚、初次轻微违法、罚款与违法情节不相当、违法所得很少但罚款很高、反映了一年没动静</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>做梦、梦见、梦到、梦境、梦里、噩梦、美梦、梦话、梦游、白日梦、噩梦惊醒、假设、假如、假若、倘若、如若、设若、假定、如果我是、假设情况、模拟场景、虚拟案例、想象一下、假如说、我举个例子、假设一下、譬如、狼人杀、杀人游戏、剧本杀、电视剧里、电影里、小说里、游戏里、剧本里、情节里、虚构故事、算了不</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>传销、层级返利、寻衅滋事、酒驾、醉驾、毒驾、肇事逃逸、强奸、猥亵、放火、爆炸、投毒、高空抛物、赌博、赌场、盗窃、诈骗、杀猪盘、刷单诈骗、冒充公检法、贩毒、运毒、藏毒、吸毒、溜冰、打K、笑气、上头烟、电子烟、拒不支付劳动报酬、逃匿</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>打人、砍人、捅人、伤人、持刀、持械、群殴、斗殴、闹事、打伤、砍伤、捅伤、打架、动刀子、流血、拉人头、交会费、发展下线、洗脑、偷电瓶、偷车、顺走、撬门、扒手、偷钢筋、偷电动车、被骗、骗钱、保健品诈骗、冒充、丢了、进贼、小偷、贼、贵重、跑路、跑了、失联、失踪、找不到人、关机、电话打不通、包工头跑路、REGEX:欠.*工资|拖.*工资|赖.*工资、REGEX:逃.*匿|跑.*路|失.*联、REGEX:顺.*(电瓶|车|东西)|偷.*(电瓶|车|东西)、REGEX:搞.*传销|拉.*人头|洗.*脑、REGEX:吸.*毒|溜.*冰|贩.*毒、REGEX:高空.*(抛|扔|丢)、REGEX:非.*法.*采矿|偷.*挖|盗.*采</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>污染、排污、排黑水、河水变黑、非法采矿、偷挖沙石、毁林、开荒、食物中毒、过期食品、三无、黑作坊、地沟油、疫苗、腹泻、非法添加、病死猪、补贴、国资流失、土地出让、社保基金、医保基金、套取、挪用、被吞、英烈、烈士陵园、诋毁英雄、绝迹、被猎光、小吃街、毒跑道、耕地</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>呛人、垃圾乱倒、乱砍树、水发臭、冒黑烟、粉尘、噪音、倾倒渣土、填埋垃圾、废水、污水、渗坑、暗管、偷排、挖山、挖空、挖沙子、采砂、养殖、拉肚子、都投诉、一直没人管、多次反映、没人处理、反复举报、众多消费者、我们都、全村都、味道刺鼻、砍树、REGEX:养猪场.(排污|排黑水|排废水)|猪粪.乱倒、REGEX:毒跑道|塑胶跑道.异味|学校.跑道.臭、REGEX:挖山.采矿|偷挖.沙石、REGEX:树林.被砍|毁林.开荒|非法.伐木、REGEX:河水.(变黑|发臭)|空气.呛人、REGEX:垃圾.(乱倒|填埋)|建筑垃圾.堆放</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>拖欠工资、欠薪、工伤不赔、赡养费、抚养费、医药费、农民工、残疾人、老人、低保、五保户、困难户、没钱打官司、请不起律师、不懂法、没证据、欠条、不养爹妈、儿女不管、丢下不管、赖账</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>房子漏水、墙壁发霉、跳闸、门柱、放线错、找不着、丢下孩子不管、电话打不通、欠我、没签合同、干杂活、不赔钱、不赔、不给钱、不给结、赖工资、合同纠纷、物业、证人、作证、REGEX:建房.(质量差|漏水|裂缝)|盖房.纠纷、REGEX:老人.(没人管|没人养|赡养)、REGEX:抚养费.不给|前夫.不给.抚养费、REGEX:装修.(出问题|质量差)|包工.纠纷、REGEX:工伤.*(不赔|没人管)|确认劳动关系</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>小过重罚、首违不罚、同案不同罚、不作为、乱作为、钓鱼执法、以罚代管、程序违法、暴力执法、强拆、保护伞、通风报信、久拖不决、推诿扯皮</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>罚款太重、张口就罚、罚得太狠、罚我、小本生意、违法所得少罚款高、没人管、形式主义、投诉没用、没动静、石沉大海、扯皮、迟迟不办、拖着、走过场、整改、走过场、包庇、纵容、今天拆明天建、不亮证、罚款不开票、没给听证机会、没告知申辩权、不出示执法证、敷衍塞责、材料反复交、奇葩证明、踢皮球、一刀切、REGEX:首违.(免罚|不罚|从轻)|首次.免罚、REGEX:过罚.(不当|相当)|小过.重罚|罚款.太重、REGEX:同案.(不同罚|不同处理)|选择性.执法、REGEX:程序.(违法|不当)|不出示.证件、REGEX:推诿.扯皮|踢皮球|久拖.*不决|不作为</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -120,7 +126,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -133,6 +139,7 @@
       <sz val="16"/>
       <color theme="1"/>
       <name val="黑体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -140,6 +147,7 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -167,6 +175,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="黑体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -206,14 +222,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -482,14 +498,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.08984375" customWidth="1"/>
     <col min="2" max="4" width="28.36328125" customWidth="1"/>
+    <col min="5" max="5" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -502,62 +519,71 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="7" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" s="2" customFormat="1" ht="270" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" s="2" customFormat="1" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="2" customFormat="1" ht="305" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="B3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="5"/>
+    </row>
+    <row r="4" spans="1:5" s="2" customFormat="1" ht="272" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="5"/>
+    </row>
+    <row r="5" spans="1:5" s="2" customFormat="1" ht="250" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" s="2" customFormat="1" ht="305" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" s="2" customFormat="1" ht="272" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" s="2" customFormat="1" ht="250" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>18</v>
+      <c r="B5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>12</v>
       </c>
+      <c r="E5" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D5" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/关键词库.xlsx
+++ b/关键词库.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Onesummer_D\Learning\Competitons\TiaoZhanBei\项目\法学产出物\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AFE80B4-EA63-40D5-A0DD-CE6FA3968E68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{510E46B2-4F1C-4753-B9B0-4CCF3711EA79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5020" yWindow="5880" windowWidth="19200" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4110" yWindow="3520" windowWidth="19200" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -90,35 +90,35 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>传销、层级返利、寻衅滋事、酒驾、醉驾、毒驾、肇事逃逸、强奸、猥亵、放火、爆炸、投毒、高空抛物、赌博、赌场、盗窃、诈骗、杀猪盘、刷单诈骗、冒充公检法、贩毒、运毒、藏毒、吸毒、溜冰、打K、笑气、上头烟、电子烟、拒不支付劳动报酬、逃匿</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>打人、砍人、捅人、伤人、持刀、持械、群殴、斗殴、闹事、打伤、砍伤、捅伤、打架、动刀子、流血、拉人头、交会费、发展下线、洗脑、偷电瓶、偷车、顺走、撬门、扒手、偷钢筋、偷电动车、被骗、骗钱、保健品诈骗、冒充、丢了、进贼、小偷、贼、贵重、跑路、跑了、失联、失踪、找不到人、关机、电话打不通、包工头跑路、REGEX:欠.*工资|拖.*工资|赖.*工资、REGEX:逃.*匿|跑.*路|失.*联、REGEX:顺.*(电瓶|车|东西)|偷.*(电瓶|车|东西)、REGEX:搞.*传销|拉.*人头|洗.*脑、REGEX:吸.*毒|溜.*冰|贩.*毒、REGEX:高空.*(抛|扔|丢)、REGEX:非.*法.*采矿|偷.*挖|盗.*采</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>污染、排污、排黑水、河水变黑、非法采矿、偷挖沙石、毁林、开荒、食物中毒、过期食品、三无、黑作坊、地沟油、疫苗、腹泻、非法添加、病死猪、补贴、国资流失、土地出让、社保基金、医保基金、套取、挪用、被吞、英烈、烈士陵园、诋毁英雄、绝迹、被猎光、小吃街、毒跑道、耕地</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>呛人、垃圾乱倒、乱砍树、水发臭、冒黑烟、粉尘、噪音、倾倒渣土、填埋垃圾、废水、污水、渗坑、暗管、偷排、挖山、挖空、挖沙子、采砂、养殖、拉肚子、都投诉、一直没人管、多次反映、没人处理、反复举报、众多消费者、我们都、全村都、味道刺鼻、砍树、REGEX:养猪场.(排污|排黑水|排废水)|猪粪.乱倒、REGEX:毒跑道|塑胶跑道.异味|学校.跑道.臭、REGEX:挖山.采矿|偷挖.沙石、REGEX:树林.被砍|毁林.开荒|非法.伐木、REGEX:河水.(变黑|发臭)|空气.呛人、REGEX:垃圾.(乱倒|填埋)|建筑垃圾.堆放</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>拖欠工资、欠薪、工伤不赔、赡养费、抚养费、医药费、农民工、残疾人、老人、低保、五保户、困难户、没钱打官司、请不起律师、不懂法、没证据、欠条、不养爹妈、儿女不管、丢下不管、赖账</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>房子漏水、墙壁发霉、跳闸、门柱、放线错、找不着、丢下孩子不管、电话打不通、欠我、没签合同、干杂活、不赔钱、不赔、不给钱、不给结、赖工资、合同纠纷、物业、证人、作证、REGEX:建房.(质量差|漏水|裂缝)|盖房.纠纷、REGEX:老人.(没人管|没人养|赡养)、REGEX:抚养费.不给|前夫.不给.抚养费、REGEX:装修.(出问题|质量差)|包工.纠纷、REGEX:工伤.*(不赔|没人管)|确认劳动关系</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>小过重罚、首违不罚、同案不同罚、不作为、乱作为、钓鱼执法、以罚代管、程序违法、暴力执法、强拆、保护伞、通风报信、久拖不决、推诿扯皮</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>罚款太重、张口就罚、罚得太狠、罚我、小本生意、违法所得少罚款高、没人管、形式主义、投诉没用、没动静、石沉大海、扯皮、迟迟不办、拖着、走过场、整改、走过场、包庇、纵容、今天拆明天建、不亮证、罚款不开票、没给听证机会、没告知申辩权、不出示执法证、敷衍塞责、材料反复交、奇葩证明、踢皮球、一刀切、REGEX:首违.(免罚|不罚|从轻)|首次.免罚、REGEX:过罚.(不当|相当)|小过.重罚|罚款.太重、REGEX:同案.(不同罚|不同处理)|选择性.执法、REGEX:程序.(违法|不当)|不出示.证件、REGEX:推诿.扯皮|踢皮球|久拖.*不决|不作为</t>
+    <t>小过重罚、首违不罚、同案不同罚、不作为、乱作为、钓鱼执法、以罚代管、程序违法、暴力执法、强拆、保护伞、通风报信、久拖不决、推诿扯皮、出示证件、执法证、搬上车、野蛮执法、穿制服、违建、半年未拆、占排水沟、装修好住人、卫生费、停水、收费依据、乱收费、占道经营、有证、区别对待、只罚我、转了一个多月、石沉大海、罚、重罚、冤枉、监管局、12345、城管、市场监督管理局、工商、踢皮球</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>拖欠工资、欠薪、工伤不赔、赡养费、抚养费、医药费、农民工、残疾人、低保、五保户、困难户、没钱打官司、请不起律师、不懂法、没证据、欠条、不养爹妈、儿女不管、丢下不管、赖账、关门、停业、装修一半、停工、材料款、自建房、娶媳妇、不给赡养费、不孝、尽孝、老伴去世、砌砖、搭架子、农业大棚、苦力、拖着、不给钱、欠工资、欠、拖欠、血汗钱、工钱、劳务费、劳动报酬、工资被拖欠、工资、辛苦钱</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>房子漏水、墙壁发霉、跳闸、门柱、放线错、一分没给、找不着、丢下孩子不管、电话打不通、欠我、没签合同、干杂活、跑路、赖着、赖账、讨要、讨薪、催要、索要、工资没发、钱没给、拿不到钱、被欠钱、不赔钱、不赔、不发、扣着、电话打不通、打电话不接、要回来、不给结、赖工资、合同纠纷、健身房、培训机构、地面找平、装修公司、锁门、英语班、关机、找借口、物业、水电工、包工头、证人、作证、REGEX:建房.(质量差|漏水|裂缝)|盖房.纠纷、REGEX:老人.(没人管|没人养|赡养)、REGEX:抚养费.不给|前夫.不给.抚养费、REGEX:装修.(出问题|质量差)|包工.纠纷、REGEX:工伤.*(不赔|没人管)|确认劳动关系、REGEX:健身房.(关门|锁门|装修)|培训机构.(倒闭|跑路)|英语.(班|课)、REGEX:装修.(一半|停工|不干)|地面.(找平|没做)|公司.(锁门|关门)、REGEX:不给.(赡养费|抚养费)|不孝.子女|尽孝|82岁|老伴.去世、REGEX:水电工|砌砖|搭架子|大棚.(项目|干活)|苦力.*(人|工)、REGEX:下水道.(堵|返水)|污水.(返|冒)|臭.(家里|楼道)|转.(多月|来回)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>打人、动手、砍人、捅人、伤人、群殴、警察、报复、斗殴、遗址、闹事、打伤、砍伤、捅伤、打架、动刀子、流血、拉人头、交会费、发展下线、洗脑、偷电瓶、恶霸、偷车、偷了、顺走、撬门、扒手、偷钢筋、偷电动车、被骗、骗钱、保健品诈骗、冒充、丢了、贵重、跑路、跑了、失联、失踪、找不到人、人间蒸发、包工头跑路、REGEX:欠.*工资|拖.*工资|赖.*工资、REGEX:逃.*匿|跑.*路|失.*联、REGEX:顺.*(电瓶|车|东西)|偷.*(电瓶|车|东西)、REGEX:搞.*传销|拉.*人头|洗.*脑、REGEX:吸.*毒|溜.*冰|贩.*毒、REGEX:高空.*(抛|扔|丢)、REGEX:非.*法.*采矿|偷.*挖|盗.*采、REGEX:威胁.(弄死|打断腿|收拾|敢告)|放话.(找人|打你)、REGEX:拉车门|车内.(现金|财物|名酒)|地下室.(被盗|入侵)、REGEX:倒车.(撞|碾)|撞.(协警|交警)|逆行.逃逸、REGEX:套取.(资金|补偿款|工程款)|挪用.(集体|公款)、REGEX:扎.轮胎|泄愤|毁坏.财物、REGEX:虐待.(孩子|未成年人)|家暴.(轻伤|孩子)、REGEX:假.调解|套取.公积金|配合.(假诉讼|虚假)、REGEX:假酒|私自.灌装|勾兑.(白酒|酒水)、REGEX:出售.(信息|业主)|骚扰.电话|泄露.(个人信息|账户)、REGEX:投资.理财|线下.取现|无法.取现|账户.*冻结、弄死、棍子、威胁</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>污染、排污、排黑水、河水变黑、偷挖沙石、毁林、开荒、食物中毒、过期食品、三无、黑作坊、地沟油、疫苗、腹泻、非法添加、病死猪、补贴、国资流失、土地出让、社保、医保、英烈、烈士陵园、诋毁英雄、绝迹、被猎光、小吃街、毒跑道、耕地、KTV、震得、噪音、烧垃圾、黑烟滚滚、半夜烧、塑料、破衣服、饮用水、水井、沉淀物、养猪场、猪粪、拓印、刻字、老宅、拆除、历史建筑、雕花、青砖、硬化、粮田、耕地、电鱼、禁渔期、翻白肚、绝户网、下水道、污水返、臭、垃圾、化学、化工厂、烧、遗址</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>呛人、乱砍树、水发臭、冒黑烟、挖矿、泥浆、泥石、拆迁、工地、粉尘、噪音、倾倒渣土、灰、灰尘、废水、污水、粪水、渗坑、暗管、偷排、挖空、挖沙子、采砂、毒土、烂菜叶、养殖、拉肚子、都投诉、一直没人管、多次反映、没人处理、反复举报、众多消费者、捕鸟、捕猎、偷鸟、我们都、全村都、刺鼻、怪味、臭气熏天、采矿、砍树、REGEX:养猪场.(排污|排黑水|排废水)|猪粪.乱倒、REGEX:毒跑道|塑胶跑道.异味|学校.跑道.臭、REGEX:挖山.采矿|偷挖.沙石、REGEX:树林.被砍|毁林.开荒|非法.伐木、REGEX:河水.(变黑|发臭)|空气.呛人、REGEX:垃圾.(乱倒|填埋)|建筑垃圾.堆放、REGEX:KTV.(噪音|扰民)|低音炮.(震|响)|晚上.(唱歌|音乐)、REGEX:烧.垃圾|黑烟.(滚滚|大)|半夜.(烧|点火)|塑料.(烧|味)、REGEX:饮用水.(污染|变黄)|水井.(黄|臭|沉淀)|养猪场.(排污|粪水)、REGEX:拓印|刻字.(到此一游)|老宅.(拆除|拆)|历史建筑.(破坏)、REGEX:耕地.(硬化|水泥)|停车场.(货车)|口粮田.(占用)、REGEX:电鱼|小船.(晚上|半夜)|禁渔期.(捕鱼)|鱼.*(翻白肚|死光)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>传销、层级返利、寻衅滋事、酒驾、醉驾、毒驾、肇事、强奸、猥亵、放火、爆炸、引燃、投毒、闪爆、高空抛物、赌博、赌场、盗窃、诈骗、杀猪盘、刷单诈骗、冒充公检法、贩毒、运毒、藏毒、吸毒、溜冰、打K、笑气、上头烟、电子烟、拒不支付劳动报酬、逃匿、恐吓、打断、找人收拾、敢告、挖山、采矿住院、轻伤、重伤、持刀、持械、非法拘禁、绑架、勒索、故意伤害、聚众斗殴、拉车门、车内财物、地下室、凌晨、半夜、偷走、醉驾、倒车、撞伤、协警、逃逸、套取、挪用、集体资金、补偿款、工程款、扎轮胎、泄愤、毁坏财物、虐待、家暴、轻伤二级、假调解、套取、公积金、配合、假酒、灌装、私自、勾兑、出售信息、骚扰电话、业主信息、泄露、投资、理财、取现、账户冻结、进贼、小偷、贼、虚报、伪造、文物、公安、盗墓、罪、非法、贿赂、行贿、刑、逃逸、骗子、骗、违法</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>罚款太重、张口就罚、罚得太狠、罚我、罚款、罚单、罚不起、小本生意、违法所得少罚款高、罚得太狠、没人管、形式主义、投诉没用、没动静、石沉大海、扯皮、超范围经营、迟迟不办、拖着、一直不、走过场、整改、走过场、包庇、纵容、抽烟、孕妇、鼻炎、烟雾缭绕、网咖、无证经营、今天拆明天建、不亮证、罚款不开票、管不了、发票、没给听证机会、广告、没告知申辩权、不出示执法证、敷衍塞责、材料反复交、没有依据、奇葩证明、物业、烟灰缸、烟头、遗留、一刀切、REGEX:首违.(免罚|不罚|从轻)|首次.免罚、REGEX:过罚.(不当|相当)|小过.重罚|罚款.太重、REGEX:同案.(不同罚|不同处理)|选择性.执法、REGEX:程序.(违法|不当)|不出示.证件、REGEX:推诿.扯皮|踢皮球|久拖.*不决|不作为、REGEX:抽烟.(楼道|厕所|餐厅)|孕妇.(抽烟|烟味)|鼻炎.(烟|熏)、REGEX:不出示.(证件|执法证)|搬.上车|野蛮.执法|穿制服.(没收)、REGEX:违建.(半年|久拖|未拆)|占.(排水沟|过道)|装修.(住人|完工)、REGEX:卫生费.(500|高额)|停水.(威胁|不交)|收费.(依据|标准)、REGEX:占道.(经营|摆摊)|有证.(不罚)|区别对待|只罚.(我|我不罚他)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -528,10 +528,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>9</v>
@@ -545,10 +545,10 @@
         <v>5</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>10</v>
@@ -560,10 +560,10 @@
         <v>7</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>11</v>
@@ -575,7 +575,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>21</v>

--- a/关键词库.xlsx
+++ b/关键词库.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Onesummer_D\Learning\Competitons\TiaoZhanBei\项目\法学产出物\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{510E46B2-4F1C-4753-B9B0-4CCF3711EA79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B2A7347-F352-4367-A36E-6A489F300B27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4110" yWindow="3520" windowWidth="19200" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2550" yWindow="5120" windowWidth="23710" windowHeight="10950" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -102,10 +102,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>打人、动手、砍人、捅人、伤人、群殴、警察、报复、斗殴、遗址、闹事、打伤、砍伤、捅伤、打架、动刀子、流血、拉人头、交会费、发展下线、洗脑、偷电瓶、恶霸、偷车、偷了、顺走、撬门、扒手、偷钢筋、偷电动车、被骗、骗钱、保健品诈骗、冒充、丢了、贵重、跑路、跑了、失联、失踪、找不到人、人间蒸发、包工头跑路、REGEX:欠.*工资|拖.*工资|赖.*工资、REGEX:逃.*匿|跑.*路|失.*联、REGEX:顺.*(电瓶|车|东西)|偷.*(电瓶|车|东西)、REGEX:搞.*传销|拉.*人头|洗.*脑、REGEX:吸.*毒|溜.*冰|贩.*毒、REGEX:高空.*(抛|扔|丢)、REGEX:非.*法.*采矿|偷.*挖|盗.*采、REGEX:威胁.(弄死|打断腿|收拾|敢告)|放话.(找人|打你)、REGEX:拉车门|车内.(现金|财物|名酒)|地下室.(被盗|入侵)、REGEX:倒车.(撞|碾)|撞.(协警|交警)|逆行.逃逸、REGEX:套取.(资金|补偿款|工程款)|挪用.(集体|公款)、REGEX:扎.轮胎|泄愤|毁坏.财物、REGEX:虐待.(孩子|未成年人)|家暴.(轻伤|孩子)、REGEX:假.调解|套取.公积金|配合.(假诉讼|虚假)、REGEX:假酒|私自.灌装|勾兑.(白酒|酒水)、REGEX:出售.(信息|业主)|骚扰.电话|泄露.(个人信息|账户)、REGEX:投资.理财|线下.取现|无法.取现|账户.*冻结、弄死、棍子、威胁</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>污染、排污、排黑水、河水变黑、偷挖沙石、毁林、开荒、食物中毒、过期食品、三无、黑作坊、地沟油、疫苗、腹泻、非法添加、病死猪、补贴、国资流失、土地出让、社保、医保、英烈、烈士陵园、诋毁英雄、绝迹、被猎光、小吃街、毒跑道、耕地、KTV、震得、噪音、烧垃圾、黑烟滚滚、半夜烧、塑料、破衣服、饮用水、水井、沉淀物、养猪场、猪粪、拓印、刻字、老宅、拆除、历史建筑、雕花、青砖、硬化、粮田、耕地、电鱼、禁渔期、翻白肚、绝户网、下水道、污水返、臭、垃圾、化学、化工厂、烧、遗址</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -114,11 +110,15 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>传销、层级返利、寻衅滋事、酒驾、醉驾、毒驾、肇事、强奸、猥亵、放火、爆炸、引燃、投毒、闪爆、高空抛物、赌博、赌场、盗窃、诈骗、杀猪盘、刷单诈骗、冒充公检法、贩毒、运毒、藏毒、吸毒、溜冰、打K、笑气、上头烟、电子烟、拒不支付劳动报酬、逃匿、恐吓、打断、找人收拾、敢告、挖山、采矿住院、轻伤、重伤、持刀、持械、非法拘禁、绑架、勒索、故意伤害、聚众斗殴、拉车门、车内财物、地下室、凌晨、半夜、偷走、醉驾、倒车、撞伤、协警、逃逸、套取、挪用、集体资金、补偿款、工程款、扎轮胎、泄愤、毁坏财物、虐待、家暴、轻伤二级、假调解、套取、公积金、配合、假酒、灌装、私自、勾兑、出售信息、骚扰电话、业主信息、泄露、投资、理财、取现、账户冻结、进贼、小偷、贼、虚报、伪造、文物、公安、盗墓、罪、非法、贿赂、行贿、刑、逃逸、骗子、骗、违法</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>罚款太重、张口就罚、罚得太狠、罚我、罚款、罚单、罚不起、小本生意、违法所得少罚款高、罚得太狠、没人管、形式主义、投诉没用、没动静、石沉大海、扯皮、超范围经营、迟迟不办、拖着、一直不、走过场、整改、走过场、包庇、纵容、抽烟、孕妇、鼻炎、烟雾缭绕、网咖、无证经营、今天拆明天建、不亮证、罚款不开票、管不了、发票、没给听证机会、广告、没告知申辩权、不出示执法证、敷衍塞责、材料反复交、没有依据、奇葩证明、物业、烟灰缸、烟头、遗留、一刀切、REGEX:首违.(免罚|不罚|从轻)|首次.免罚、REGEX:过罚.(不当|相当)|小过.重罚|罚款.太重、REGEX:同案.(不同罚|不同处理)|选择性.执法、REGEX:程序.(违法|不当)|不出示.证件、REGEX:推诿.扯皮|踢皮球|久拖.*不决|不作为、REGEX:抽烟.(楼道|厕所|餐厅)|孕妇.(抽烟|烟味)|鼻炎.(烟|熏)、REGEX:不出示.(证件|执法证)|搬.上车|野蛮.执法|穿制服.(没收)、REGEX:违建.(半年|久拖|未拆)|占.(排水沟|过道)|装修.(住人|完工)、REGEX:卫生费.(500|高额)|停水.(威胁|不交)|收费.(依据|标准)、REGEX:占道.(经营|摆摊)|有证.(不罚)|区别对待|只罚.(我|我不罚他)</t>
+    <t>传销、层级返利、寻衅滋事、酒驾、醉驾、毒驾、肇事、强奸、猥亵、放火、爆炸、引燃、投毒、闪爆、高空抛物、赌博、赌场、盗窃、诈骗、杀猪盘、刷单诈骗、冒充公检法、贩毒、运毒、藏毒、吸毒、溜冰、打K、笑气、上头烟、电子烟、拒不支付劳动报酬、逃匿、恐吓、打断、找人收拾、敢告、挖山、采矿住院、轻伤、重伤、持刀、持械、非法拘禁、绑架、勒索、故意伤害、聚众斗殴、拉车门、车内财物、地下室、凌晨、半夜、偷走、醉驾、倒车、撞伤、协警、逃逸、套取、挪用、集体资金、补偿款、工程款、扎轮胎、泄愤、毁坏财物、虐待、家暴、轻伤二级、假调解、套取、冒用、盗刷、白条、公积金、配合、假酒、灌装、私自、勾兑、出售信息、骚扰电话、业主信息、泄露、投资、理财、取现、账户冻结、进贼、小偷、贼、虚报、伪造、文物、公安、盗墓、罪、非法、贿赂、行贿、刑、逃逸、骗子、骗、违法</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>打人、动手、砍人、捅人、伤人、群殴、警察、报复、斗殴、遗址、闹事、打伤、砍伤、捅伤、打架、动刀子、流血、拉人头、交会费、发展下线、洗脑、偷电瓶、恶霸、偷快递、偷车、偷了、顺走、拿走、异地消费、二维码、投票、账号、扫码、微信群、撬门、扒手、偷钢筋、偷电动车、被骗、骗钱、保健品诈骗、冒充、丢了、贵重、跑路、跑了、失联、失踪、找不到人、人间蒸发、包工头跑路、REGEX:欠.*工资|拖.*工资|赖.*工资、REGEX:逃.*匿|跑.*路|失.*联、REGEX:顺.*(电瓶|车|东西)|偷.*(电瓶|车|东西)、REGEX:搞.*传销|拉.*人头|洗.*脑、REGEX:吸.*毒|溜.*冰|贩.*毒、REGEX:高空.*(抛|扔|丢)、REGEX:非.*法.*采矿|偷.*挖|盗.*采、REGEX:威胁.(弄死|打断腿|收拾|敢告)|放话.(找人|打你)、REGEX:拉车门|车内.(现金|财物|名酒)|地下室.(被盗|入侵)、REGEX:倒车.(撞|碾)|撞.(协警|交警)|逆行.逃逸、REGEX:套取.(资金|补偿款|工程款)|挪用.(集体|公款)、REGEX:扎.轮胎|泄愤|毁坏.财物、REGEX:虐待.(孩子|未成年人)|家暴.(轻伤|孩子)、REGEX:假.调解|套取.公积金|配合.(假诉讼|虚假)、REGEX:假酒|私自.灌装|勾兑.(白酒|酒水)、REGEX:出售.(信息|业主)|骚扰.电话|泄露.(个人信息|账户)、REGEX:投资.理财|线下.取现|无法.取现|账户.*冻结、弄死、棍子、威胁</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>罚款太重、张口就罚、罚得太狠、罚我、罚款、罚单、罚不起、小本生意、违法所得少罚款高、罚得太狠、没人管、形式主义、投诉没用、没动静、石沉大海、扯皮、超范围经营、迟迟不办、拖着、一直不、走过场、整改、走过场、包庇、纵容、抽烟、孕妇、鼻炎、烟雾缭绕、网咖、无证经营、今天拆明天建、不亮证、罚款不开票、管不了、发票、没给听证机会、广告、没告知申辩权、不出示执法证、敷衍塞责、材料反复交、没有依据、奇葩证明、房产证、物业、烟灰缸、烟头、遗留、一刀切、REGEX:首违.(免罚|不罚|从轻)|首次.免罚、REGEX:过罚.(不当|相当)|小过.重罚|罚款.太重、REGEX:同案.(不同罚|不同处理)|选择性.执法、REGEX:程序.(违法|不当)|不出示.证件、REGEX:推诿.扯皮|踢皮球|久拖.*不决|不作为、REGEX:抽烟.(楼道|厕所|餐厅)|孕妇.(抽烟|烟味)|鼻炎.(烟|熏)、REGEX:不出示.(证件|执法证)|搬.上车|野蛮.执法|穿制服.(没收)、REGEX:违建.(半年|久拖|未拆)|占.(排水沟|过道)|装修.(住人|完工)、REGEX:卫生费.(500|高额)|停水.(威胁|不交)|收费.(依据|标准)、REGEX:占道.(经营|摆摊)|有证.(不罚)|区别对待|只罚.(我|我不罚他)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -528,10 +528,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>17</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>9</v>
@@ -545,10 +545,10 @@
         <v>5</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>18</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>19</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>10</v>

--- a/关键词库.xlsx
+++ b/关键词库.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Onesummer_D\Learning\Competitons\TiaoZhanBei\项目\法学产出物\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B2A7347-F352-4367-A36E-6A489F300B27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD38AB2-953E-4B21-96EF-CE874B39403D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2550" yWindow="5120" windowWidth="23710" windowHeight="10950" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2880" yWindow="5080" windowWidth="23710" windowHeight="10950" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -102,23 +102,23 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>污染、排污、排黑水、河水变黑、偷挖沙石、毁林、开荒、食物中毒、过期食品、三无、黑作坊、地沟油、疫苗、腹泻、非法添加、病死猪、补贴、国资流失、土地出让、社保、医保、英烈、烈士陵园、诋毁英雄、绝迹、被猎光、小吃街、毒跑道、耕地、KTV、震得、噪音、烧垃圾、黑烟滚滚、半夜烧、塑料、破衣服、饮用水、水井、沉淀物、养猪场、猪粪、拓印、刻字、老宅、拆除、历史建筑、雕花、青砖、硬化、粮田、耕地、电鱼、禁渔期、翻白肚、绝户网、下水道、污水返、臭、垃圾、化学、化工厂、烧、遗址</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>呛人、乱砍树、水发臭、冒黑烟、挖矿、泥浆、泥石、拆迁、工地、粉尘、噪音、倾倒渣土、灰、灰尘、废水、污水、粪水、渗坑、暗管、偷排、挖空、挖沙子、采砂、毒土、烂菜叶、养殖、拉肚子、都投诉、一直没人管、多次反映、没人处理、反复举报、众多消费者、捕鸟、捕猎、偷鸟、我们都、全村都、刺鼻、怪味、臭气熏天、采矿、砍树、REGEX:养猪场.(排污|排黑水|排废水)|猪粪.乱倒、REGEX:毒跑道|塑胶跑道.异味|学校.跑道.臭、REGEX:挖山.采矿|偷挖.沙石、REGEX:树林.被砍|毁林.开荒|非法.伐木、REGEX:河水.(变黑|发臭)|空气.呛人、REGEX:垃圾.(乱倒|填埋)|建筑垃圾.堆放、REGEX:KTV.(噪音|扰民)|低音炮.(震|响)|晚上.(唱歌|音乐)、REGEX:烧.垃圾|黑烟.(滚滚|大)|半夜.(烧|点火)|塑料.(烧|味)、REGEX:饮用水.(污染|变黄)|水井.(黄|臭|沉淀)|养猪场.(排污|粪水)、REGEX:拓印|刻字.(到此一游)|老宅.(拆除|拆)|历史建筑.(破坏)、REGEX:耕地.(硬化|水泥)|停车场.(货车)|口粮田.(占用)、REGEX:电鱼|小船.(晚上|半夜)|禁渔期.(捕鱼)|鱼.*(翻白肚|死光)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>传销、层级返利、寻衅滋事、酒驾、醉驾、毒驾、肇事、强奸、猥亵、放火、爆炸、引燃、投毒、闪爆、高空抛物、赌博、赌场、盗窃、诈骗、杀猪盘、刷单诈骗、冒充公检法、贩毒、运毒、藏毒、吸毒、溜冰、打K、笑气、上头烟、电子烟、拒不支付劳动报酬、逃匿、恐吓、打断、找人收拾、敢告、挖山、采矿住院、轻伤、重伤、持刀、持械、非法拘禁、绑架、勒索、故意伤害、聚众斗殴、拉车门、车内财物、地下室、凌晨、半夜、偷走、醉驾、倒车、撞伤、协警、逃逸、套取、挪用、集体资金、补偿款、工程款、扎轮胎、泄愤、毁坏财物、虐待、家暴、轻伤二级、假调解、套取、冒用、盗刷、白条、公积金、配合、假酒、灌装、私自、勾兑、出售信息、骚扰电话、业主信息、泄露、投资、理财、取现、账户冻结、进贼、小偷、贼、虚报、伪造、文物、公安、盗墓、罪、非法、贿赂、行贿、刑、逃逸、骗子、骗、违法</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>打人、动手、砍人、捅人、伤人、群殴、警察、报复、斗殴、遗址、闹事、打伤、砍伤、捅伤、打架、动刀子、流血、拉人头、交会费、发展下线、洗脑、偷电瓶、恶霸、偷快递、偷车、偷了、顺走、拿走、异地消费、二维码、投票、账号、扫码、微信群、撬门、扒手、偷钢筋、偷电动车、被骗、骗钱、保健品诈骗、冒充、丢了、贵重、跑路、跑了、失联、失踪、找不到人、人间蒸发、包工头跑路、REGEX:欠.*工资|拖.*工资|赖.*工资、REGEX:逃.*匿|跑.*路|失.*联、REGEX:顺.*(电瓶|车|东西)|偷.*(电瓶|车|东西)、REGEX:搞.*传销|拉.*人头|洗.*脑、REGEX:吸.*毒|溜.*冰|贩.*毒、REGEX:高空.*(抛|扔|丢)、REGEX:非.*法.*采矿|偷.*挖|盗.*采、REGEX:威胁.(弄死|打断腿|收拾|敢告)|放话.(找人|打你)、REGEX:拉车门|车内.(现金|财物|名酒)|地下室.(被盗|入侵)、REGEX:倒车.(撞|碾)|撞.(协警|交警)|逆行.逃逸、REGEX:套取.(资金|补偿款|工程款)|挪用.(集体|公款)、REGEX:扎.轮胎|泄愤|毁坏.财物、REGEX:虐待.(孩子|未成年人)|家暴.(轻伤|孩子)、REGEX:假.调解|套取.公积金|配合.(假诉讼|虚假)、REGEX:假酒|私自.灌装|勾兑.(白酒|酒水)、REGEX:出售.(信息|业主)|骚扰.电话|泄露.(个人信息|账户)、REGEX:投资.理财|线下.取现|无法.取现|账户.*冻结、弄死、棍子、威胁</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>罚款太重、张口就罚、罚得太狠、罚我、罚款、罚单、罚不起、小本生意、违法所得少罚款高、罚得太狠、没人管、形式主义、投诉没用、没动静、石沉大海、扯皮、超范围经营、迟迟不办、拖着、一直不、走过场、整改、走过场、包庇、纵容、抽烟、孕妇、鼻炎、烟雾缭绕、网咖、无证经营、今天拆明天建、不亮证、罚款不开票、管不了、发票、没给听证机会、广告、没告知申辩权、不出示执法证、敷衍塞责、材料反复交、没有依据、奇葩证明、房产证、物业、烟灰缸、烟头、遗留、一刀切、REGEX:首违.(免罚|不罚|从轻)|首次.免罚、REGEX:过罚.(不当|相当)|小过.重罚|罚款.太重、REGEX:同案.(不同罚|不同处理)|选择性.执法、REGEX:程序.(违法|不当)|不出示.证件、REGEX:推诿.扯皮|踢皮球|久拖.*不决|不作为、REGEX:抽烟.(楼道|厕所|餐厅)|孕妇.(抽烟|烟味)|鼻炎.(烟|熏)、REGEX:不出示.(证件|执法证)|搬.上车|野蛮.执法|穿制服.(没收)、REGEX:违建.(半年|久拖|未拆)|占.(排水沟|过道)|装修.(住人|完工)、REGEX:卫生费.(500|高额)|停水.(威胁|不交)|收费.(依据|标准)、REGEX:占道.(经营|摆摊)|有证.(不罚)|区别对待|只罚.(我|我不罚他)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>传销、层级返利、寻衅滋事、酒驾、醉驾、毒驾、肇事、强奸、猥亵、放火、爆炸、引燃、投毒、闪爆、高空抛物、从楼上扔、赌博、赌场、盗窃、诈骗、杀猪盘、刷单诈骗、冒充公检法、贩毒、运毒、藏毒、吸毒、溜冰、打K、笑气、上头烟、电子烟、拒不支付劳动报酬、逃匿、恐吓、打断、找人收拾、敢告、挖山、采矿住院、轻伤、重伤、持刀、持械、非法拘禁、绑架、勒索、故意伤害、聚众斗殴、拉车门、车内财物、地下室、凌晨、半夜、偷走、醉驾、倒车、撞伤、协警、逃逸、套取、挪用、集体资金、补偿款、工程款、扎轮胎、泄愤、毁坏财物、虐待、家暴、轻伤二级、假调解、套取、冒用、盗刷、白条、公积金、配合、假酒、灌装、私自、勾兑、出售信息、骚扰电话、业主信息、泄露、投资、理财、取现、账户冻结、进贼、小偷、贼、虚报、伪造、文物、公安、盗墓、罪、非法、贿赂、行贿、刑、逃逸、骗子、骗、违法、REGEX:从.*楼.*扔|从.*楼.*抛|从.*楼.*砸|高空.*抛物</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>打人、动手、砍人、捅人、伤人、群殴、警察、砸坏、砸车、报复、斗殴、遗址、闹事、打伤、砍伤、捅伤、打架、动刀子、流血、拉人头、交会费、发展下线、洗脑、偷电瓶、恶霸、偷快递、偷车、偷了、顺走、拿走、异地消费、二维码、投票、账号、扫码、扔东西、从楼上、微信群、撬门、扒手、偷钢筋、偷电动车、被骗、骗钱、保健品诈骗、冒充、丢了、贵重、跑路、跑了、失联、失踪、找不到人、人间蒸发、包工头跑路、REGEX:欠.*工资|拖.*工资|赖.*工资、REGEX:逃.*匿|跑.*路|失.*联、REGEX:顺.*(电瓶|车|东西)|偷.*(电瓶|车|东西)、REGEX:搞.*传销|拉.*人头|洗.*脑、REGEX:吸.*毒|溜.*冰|贩.*毒、REGEX:高空.*(抛|扔|丢)、REGEX:非.*法.*采矿|偷.*挖|盗.*采、REGEX:威胁.(弄死|打断腿|收拾|敢告)|放话.(找人|打你)、REGEX:拉车门|车内.(现金|财物|名酒)|地下室.(被盗|入侵)、REGEX:倒车.(撞|碾)|撞.(协警|交警)|逆行.逃逸、REGEX:套取.(资金|补偿款|工程款)|挪用.(集体|公款)、REGEX:扎.轮胎|泄愤|毁坏.财物、REGEX:虐待.(孩子|未成年人)|家暴.(轻伤|孩子)、REGEX:假.调解|套取.公积金|配合.(假诉讼|虚假)、REGEX:假酒|私自.灌装|勾兑.(白酒|酒水)、REGEX:出售.(信息|业主)|骚扰.电话|泄露.(个人信息|账户)、REGEX:投资.理财|线下.取现|无法.取现|账户.*冻结、弄死、棍子、威胁</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>污染、排污、排黑水、河水变黑、偷挖沙石、毁林、开荒、食物中毒、过期食品、三无、黑作坊、地沟油、疫苗、腹泻、非法添加、病死猪、补贴、国资流失、土地出让、社保、医保、英烈、烈士陵园、诋毁英雄、绝迹、被猎光、小吃街、毒跑道、耕地、KTV、震得、噪音、烧垃圾、黑烟滚滚、半夜烧、塑料、破衣服、饮用水、水井、沉淀物、养猪场、猪粪、拓印、刻字、老宅、拆除、历史建筑、雕花、青砖、硬化、粮田、耕地、电鱼、禁渔期、翻白肚、绝户网、下水道、污水返、臭、垃圾、化学、化工厂、烧、遗址、替代性修复、生态修复、生态公益林、惩罚性赔偿、公益诉讼公告</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>呛人、乱砍树、水发臭、冒黑烟、挖矿、泥浆、泥石、拆迁、工地、粉尘、噪音、倾倒渣土、灰、灰尘、废水、污水、粪水、渗坑、暗管、偷排、挖空、挖沙子、采砂、毒土、烂菜叶、养殖、拉肚子、都投诉、一直没人管、多次反映、没人处理、反复举报、众多消费者、捕鸟、捕猎、偷鸟、我们都、全村都、刺鼻、怪味、山体破坏、钩机、饮用水井、臭气熏天、采矿、砍树、REGEX:养猪场.(排污|排黑水|排废水)|猪粪.乱倒、REGEX:毒跑道|塑胶跑道.异味|学校.跑道.臭、REGEX:挖山.采矿|偷挖.沙石、REGEX:树林.被砍|毁林.开荒|非法.伐木、REGEX:河水.(变黑|发臭)|空气.呛人、REGEX:垃圾.(乱倒|填埋)|建筑垃圾.堆放、REGEX:KTV.(噪音|扰民)|低音炮.(震|响)|晚上.(唱歌|音乐)、REGEX:烧.垃圾|黑烟.(滚滚|大)|半夜.(烧|点火)|塑料.(烧|味)、REGEX:饮用水.(污染|变黄)|水井.(黄|臭|沉淀)|养猪场.(排污|粪水)、REGEX:拓印|刻字.(到此一游)|老宅.(拆除|拆)|历史建筑.(破坏)、REGEX:耕地.(硬化|水泥)|停车场.(货车)|口粮田.(占用)、REGEX:电鱼|小船.(晚上|半夜)|禁渔期.(捕鱼)|鱼.*(翻白肚|死光)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -528,10 +528,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>19</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>20</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>9</v>
@@ -545,10 +545,10 @@
         <v>5</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>10</v>
@@ -578,7 +578,7 @@
         <v>14</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>12</v>
